--- a/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-001_SW 검증 명세서.xlsx
+++ b/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-001_SW 검증 명세서.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -710,7 +710,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1256,6 +1256,635 @@
       <c r="G22" s="50" t="inlineStr">
         <is>
           <t>자동(unittest) — tests_system/test_st_func_swr013_swr021.py::TestSTFUNC0013SensorFaultSustainedKeepsFaultAndWarning.testSensorFaultSustainedKeepsFaultStateWithWarningCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0014</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): source_timestamp_s=1.000, ignition_on=True, sensor_fault=False, rear_left_approach_risk=True(그 외 Phase2 필드 미지정/MISSING) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>좌측 도어 확정 출력=LOCK으로 관측된다(ENG-SWE1-001 4.2절 SWR-005(a): "해당 도어의 차일드락 출력을 LOCK으로 설정해야 한다"). 비고: 억제 사유(이유코드) 기록 여부는 CycleResult가 노출하지 않아(진입점 handleCycle()의 반환 계약, ledger 갭 10) 시스템 경계에서 직접 관측할 수 없다 — 이유코드 자체는 IT-0049~0054/0079/0083에서 이미 검증됨.</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test) — SWR-005 인수 시나리오</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0014ApproachRiskLocksSingleDoor.testLeftApproachRiskTrueLocksLeftDoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0015</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): source_timestamp_s=1.000, ignition_on=True, sensor_fault=False, rear_left_approach_risk=True, fire_detected=True(동시 주입, 그 외 Phase2 필드 MISSING) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>좌측 도어=LOCK 유지(접근위험 억제가 화재발 RELEASE 요청보다 우선), 우측 도어=RELEASE(화재 트리거 단독 작용) — ENG-SWE1-001 4.2절 SWR-005(b) "해제 요청을 적용하지 않고 LOCK 상태를 유지하며 억제 사유(이유코드)를 기록" + 3장 우선순위 관계("접근위험 억제[SWR-005/006] &gt; 화재/과온/성인탑승 강제해제[SWR-017]"). [적용 한계] 원문의 "해제 요청"은 통상 운전자 수동명령(OEM-FR-001)을 뜻하나 이 채널은 Phase 2 범위 밖(ENG-SWE1-001 1.3절)이라 원시 입력으로 직접 재현 불가 — 우선순위가 더 낮은 경쟁 RELEASE 후보(SWR-017)로 "해제 요청 억제"를 간접 검증한다. 이유코드 기록 자체는 CycleResult 미노출(ledger 갭 10)로 시스템 경계 관측 불가.</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t>결정표기반 시험(우선순위 결정표) + 오류추측(상충 조건)</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0015ApproachRiskSuppressesCompetingReleaseCandidate.testLeftApproachRiskKeepsLockDespiteSimultaneousFireReleaseCandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0016</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: rear_left_approach_risk=True @ nowS=1.000(최초 억제 성립). 2주기차: rear_left_approach_risk=True(재입력을 흉내) @ nowS=11.000(경과 정확히 10.000초, "10초 이하" 경계값 자체).</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t>ENG-SWE1-001 4.2절 SWR-006(a) 원문: "10초 이하 경과한 시점에... 재입력하면... override 상태와 이유코드를 생성해야 한다." [확인 필요/갭] RawCycleInput에는 운전자 재입력(해제 명령) 채널이 없고(OEM-FR-001 미분석, ledger 갭 7 — composeReleaseReRequested()가 항상 (False, False)를 반환), CycleResult는 override 상태/이유코드 필드 자체를 노출하지 않는다(ledger 갭 10). 시스템 경계에서 관측 가능한 유일한 대리 신호(좌측 출력이 LOCK을 벗어나는지)로 판정하면, 좌측은 LOCK을 계속 유지해 요구사항 원문 기준(override 성립)을 시스템 경계에서 충족하는지 확인할 수 없다.</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis) — 10초 이내 경계(elapsed=10.000s)</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0016OverrideWithinTenSecondsUnreachableAtSystemBoundary.testReinputAtExactlyTenSecondsDoesNotProduceObservableOverrideEffect</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0017</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>SWR-006</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: rear_left_approach_risk=True @ nowS=1.000(최초 억제 성립). 2주기차: rear_left_approach_risk=True @ nowS=11.100(경과 10.100초, "10초 초과" 직후 경계값, 단위시험 test_approach_risk_override_manager.py의 10.0s/10.1s 경계와 정합).</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>override로 처리되지 않고 SWR-005의 억제(LOCK)가 그대로 적용되어야 한다(ENG-SWE1-001 4.2절 SWR-006(b)). 좌측 도어=LOCK 유지가 관측되어야 한다.</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis) — 10초 초과 경계(elapsed=10.100s)</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0017SuppressionMaintainedAfterTenSecondWindow.testReinputAfterTenPointOneSecondsKeepsSuppressionApplied</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0018</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D27" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: crash_status="NONE" @ nowS=0.000(기준 수립, 비충돌). 2주기차: crash_status="CONFIRMED" @ nowS=0.300(직전 주기로부터 300ms 경과 — 평가주기 간격 최대 스트레스 시나리오).</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>2주기차(CONFIRMED가 관측된 바로 그 평가주기)에 좌/우 확정 출력이 모두 RELEASE로 전환되어야 한다(ENG-SWE1-001 4.2절 SWR-007(a): "300 ms 이내에... RELEASE로 전환해야 한다"). 300ms 간격으로 떨어진 주기에도 지연 없이 즉시 반영되어 예산을 여유 있게 충족함을 확인한다(비고: IU-0010은 경과시간을 판정에 사용하지 않아 지연 로직 자체가 없다).</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis) — 300ms 예산 상한, 평가주기 간격 스트레스</t>
+        </is>
+      </c>
+      <c r="G27" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0018CrashConfirmedReleasesWithinBudgetUnderCycleGapStress.testCrashConfirmedObservedAtThreeHundredMsGapStillYieldsImmediateRelease</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0019</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): rear_left_approach_risk=True, crash_status="CONFIRMED"(동시 주입) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력 모두 RELEASE로 관측되어야 한다(SWR-007(a) "다른 모든 명령보다 우선하여" + 3장 우선순위 관계 "충돌 긴급해제 &gt; 접근위험 억제"). 접근위험의 LOCK 요구(priority=2)가 crash의 RELEASE 요구(priority=1)에 밀려야 한다.</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="inlineStr">
+        <is>
+          <t>결정표기반 시험(우선순위 결정표 E/F/I)</t>
+        </is>
+      </c>
+      <c r="G28" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0019CrashConfirmedOutranksApproachRisk.testCrashConfirmedReleasesLeftDoorEvenWhileApproachRiskRequestsLock</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0020</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: crash_status="CONFIRMED"(단독) @ nowS=1.000(기준 RELEASE 수립). 2주기차: crash_status="CONFIRMED"(지속) + rear_left_approach_risk=True(신규 등장) @ nowS=1.300(300ms 경과).</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t>1주기차, 2주기차 모두 좌/우 확정 출력=RELEASE로 유지되어야 한다(ENG-SWE1-001 4.2절 SWR-007(b) "이후 입력 주기에도... 유지" — 후속 주기에 접근위험이 새로 나타나도 충돌 우선순위가 계속 적용됨).</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="inlineStr">
+        <is>
+          <t>상태전이 테스트(State Transition Testing) — RELEASE 지속 연속성</t>
+        </is>
+      </c>
+      <c r="G29" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0020CrashConfirmedReleaseSustainedAcrossCycles.testReleaseRemainsWhileConfirmedPersistsEvenWhenApproachRiskAppearsLater</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0021</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="inlineStr">
+        <is>
+          <t>SWR-008</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일, 부팅 직후): crash_status="PENDING"(그 외 Phase2 필드 미지정) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t>부팅 기본값(LOCK, LOCK)이 그대로 유지되어야 한다 — SWR-007의 긴급해제가 개시되지 않아야 한다(ENG-SWE1-001 4.2절 SWR-008 "PENDING인 동안... 긴급해제를 개시하지 않고... 기존 출력 결정 로직에 따른 출력을 유지"). 비고: 본 요구사항 자체가 OEM 원문에 직접 기술되지 않은 추론 요구사항이다(ENG-SWE1-001 8장 가정 6, OEM-A 확인 필요).</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning) — crash_status=PENDING 클래스</t>
+        </is>
+      </c>
+      <c r="G30" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0021CrashPendingDoesNotPrematurelyRelease.testCrashPendingAloneKeepsBootDefaultLockedOutput</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0022</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>SWR-008</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): crash_status="PENDING", fire_detected=True(동시 주입) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 관측되어야 한다 — 단, 이 RELEASE는 crash_status(PENDING, releaseCandidate 없음)가 아니라 fire_detected(SWR-017, 독립 후보)로부터 비롯되어야 한다(ENG-SWE1-001 4.2절 SWR-008 "crash_status 판정과 무관한 기존 출력 결정 로직에 따른 출력을 유지" — PENDING이 다른 SWR의 판정을 차단하지 않음을 확인).</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test) — SWR-008/SWR-017 상호작용</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0022CrashPendingDoesNotBlockOtherIndependentLogic.testCrashPendingWithFireDetectedStillReleasesViaFireNotCrash</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0023</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: fire_detected=True @ nowS=1.000(양쪽 RELEASE 기준 수립). 2주기차: fire_detected=False, rear_left_approach_risk=False, rear_right_approach_risk=False(FF 조합) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 유지되어야 한다(ENG-SWE1-001 4.2절 SWR-009 — 접근위험이 모두 FALSE이면 양쪽 도어에 영향 없음, 검증방안의 4가지 조합 중 FF).</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) — 좌/우 접근위험 2x2(FF/FT/TF/TT) 중 FF</t>
+        </is>
+      </c>
+      <c r="G32" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0023ApproachRiskBothFalseLeavesBothDoorsUnaffected.testBothRiskFalseKeepsBothDoorsAtPriorReleasedState</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0024</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: fire_detected=True @ nowS=1.000(기준 수립). 2주기차: fire_detected=False, rear_left_approach_risk=True, rear_right_approach_risk=False(TF 조합) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t>좌측=LOCK, 우측=RELEASE(변화 없음, 독립 유지)로 관측되어야 한다(SWR-009/SWR-005(a), 검증방안 TF 조합).</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) — 좌/우 접근위험 2x2 중 TF</t>
+        </is>
+      </c>
+      <c r="G33" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0024ApproachRiskLeftTrueRightFalseAffectsOnlyLeft.testLeftRiskTrueLocksLeftOnlyWhileRightStaysReleased</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0025</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: fire_detected=True @ nowS=1.000(기준 수립). 2주기차: fire_detected=False, rear_left_approach_risk=False, rear_right_approach_risk=True(FT 조합) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t>좌측=RELEASE(변화 없음), 우측=LOCK으로 관측되어야 한다(SWR-009/SWR-005(a), 검증방안 FT 조합, 좌우 대칭 확인).</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) — 좌/우 접근위험 2x2 중 FT</t>
+        </is>
+      </c>
+      <c r="G34" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0025ApproachRiskRightTrueLeftFalseAffectsOnlyRight.testRightRiskTrueLocksRightOnlyWhileLeftStaysReleased</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0026</t>
+        </is>
+      </c>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>SWR-009</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D35" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: fire_detected=True @ nowS=1.000(기준 수립). 2주기차: fire_detected=False, rear_left_approach_risk=True, rear_right_approach_risk=True(TT 조합) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 LOCK으로 관측되어야 한다(SWR-009, 검증방안 TT 조합 — 양쪽 모두 독립적으로 LOCK 전환).</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) — 좌/우 접근위험 2x2 중 TT</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0026ApproachRiskBothTrueLocksBothDoors.testBothRiskTrueLocksBothDoorsIndependently</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0027</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일, 부팅 직후): fire_detected=True(단독, 그 외 Phase2 필드 미지정) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 전환되어야 한다(ENG-SWE1-001 4.1절 SWR-017(a) "다음 평가주기 내에... 모두 RELEASE로 전환"). 비고: 트리거 입력별 이유코드 기록(SWR-017(b))은 CycleResult 미노출(ledger 갭 10)로 시스템 경계 관측 불가 — 이유코드 자체는 IT-0062~0068에서 검증됨.</t>
+        </is>
+      </c>
+      <c r="F36" s="49" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning) — fire_detected=TRUE 단독 클래스</t>
+        </is>
+      </c>
+      <c r="G36" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0027FireDetectedAloneReleasesBothDoors.testFireDetectedTrueAloneReleasesBothDoors</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0028</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일, 부팅 직후): overtemperature_detected=True(단독) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E37" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 전환되어야 한다(SWR-017(a)). 이유코드 관측 한계는 ST-FUNC-0027과 동일(ledger 갭 10).</t>
+        </is>
+      </c>
+      <c r="F37" s="49" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning) — overtemperature_detected=TRUE 단독 클래스</t>
+        </is>
+      </c>
+      <c r="G37" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0028OvertemperatureDetectedAloneReleasesBothDoors.testOvertemperatureDetectedTrueAloneReleasesBothDoors</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0029</t>
+        </is>
+      </c>
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D38" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일, 부팅 직후): adult_present=True(단독) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 전환되어야 한다(SWR-017(a)). 이유코드 관측 한계는 ST-FUNC-0027과 동일(ledger 갭 10).</t>
+        </is>
+      </c>
+      <c r="F38" s="49" t="inlineStr">
+        <is>
+          <t>동등분할(Equivalence Partitioning) — adult_present=TRUE 단독 클래스</t>
+        </is>
+      </c>
+      <c r="G38" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0029AdultPresentAloneReleasesBothDoors.testAdultPresentTrueAloneReleasesBothDoors</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0030</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>SWR-017</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일, 부팅 직후): fire_detected=True, overtemperature_detected=True, adult_present=True(3개 모두 동시 주입) @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 유지되어야 한다(ENG-SWE1-001 4.1절 SWR-017(b) "복수 입력이 동시에 TRUE이면... 출력이 RELEASE로 유지"). 단독 클래스는 ST-FUNC-0027~0029에서 이미 검증했으므로 여기서는 복수 동시발생 대표값(전부 TRUE)만 확인한다(의미 없는 조합 전수 나열을 피함).</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) — 복수 입력 동시발생 대표값</t>
+        </is>
+      </c>
+      <c r="G39" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0030AllThreeForcedReleaseTriggersSimultaneously.testFireOvertemperatureAdultAllTrueSimultaneouslyStillReleasesBothDoors</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1994,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
     </row>
@@ -1443,17 +2072,17 @@
       </c>
       <c r="D10" s="49" t="inlineStr">
         <is>
-          <t>SWR-013, SWR-021 블랙박스 시스템 테스트(ST-FUNC-0001~0013) 전량</t>
+          <t>SWR-013, SWR-021 블랙박스 시스템 테스트(ST-FUNC-0001~0013) 전량; SWR-005, SWR-006, SWR-007, SWR-008, SWR-009, SWR-017 블랙박스 시스템 테스트(ST-FUNC-0014~0030) 전량(Phase 2, 2026-09-19 추가)</t>
         </is>
       </c>
       <c r="E10" s="49" t="inlineStr">
         <is>
-          <t>tests_system/test_st_func_swr013_swr021.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-18.txt, 13/13 Pass)</t>
+          <t>tests_system/test_st_func_swr013_swr021.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-18.txt, 13/13 Pass); tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt, 17/17 unittest 통과 — 단, ST-FUNC-0016은 QA 판정상 요구사항 원문 기준 Fail로 기록됨, ENG-SWE6-002 참조)</t>
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>실제 Vehicle/CAN/LIN/HTTP I/O, HIL, 실차 검증(OEM-SWR-001 1.2/1.3절과 동일 경계). Command Arbiter 우선순위 규칙 체인(후보 명령 채널)은 Phase1 범위 밖이라 SWR-021(a) 합격기준 비고("동일 주기 신규 명령 미반영")의 명령주입 시나리오는 시험 대상에서 제외 (candidateCommands가 항상 빈 리스트인 구조적 이유, ENG-SWE1-001 1.3절).</t>
+          <t>실제 Vehicle/CAN/LIN/HTTP I/O, HIL, 실차 검증(OEM-SWR-001 1.2/1.3절과 동일 경계). Command Arbiter 우선순위 규칙 체인(후보 명령 채널)은 Phase1 범위 밖이라 SWR-021(a) 합격기준 비고("동일 주기 신규 명령 미반영")의 명령주입 시나리오는 시험 대상에서 제외 (candidateCommands가 항상 빈 리스트인 구조적 이유, ENG-SWE1-001 1.3절). Phase2 이유코드(leftReasonCode/rightReasonCode 등)는 CycleResult가 노출하지 않아(ledger 갭 10) 시스템 경계에서 직접 관측 불가 — 이유코드 자체 검증은 ENG-SWE5-002/003(IU-0010~0013/IU-0005 실물 관측)에서 이미 완료됨. SWR-006 override(releaseReRequested 채널, OEM-FR-001 미분석, ledger 갭 7)는 시스템 경계에서 원문 그대로 재현 불가 — ST-FUNC-0016이 이 한계를 시스템 수준에서 재확인함(Fail로 기록, ENG-SWE6-002 참조).</t>
         </is>
       </c>
     </row>
@@ -1484,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1563,7 +2192,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.1 (Draft) — Phase 1 최초 작성</t>
+          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
         </is>
       </c>
     </row>
@@ -1650,6 +2279,38 @@
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>Phase 2 시스템 테스트(SWE.6) 명세 갱신 — ST-FUNC-0014~0030 신규 17건(SWR-005 2건 + SWR-006 2건[10초 경계값, 1건 구조적 갭으로 Fail 기록] + SWR-007 3건[300ms 경계값 포함] + SWR-008 2건 + SWR-009 4건[좌우 독립 전 조건 조합] + SWR-017 4건, ENG-SWE1-001 4.1/4.2절 기반 블랙박스 케이스). 진입점 InputValidationAdapter.handleCycle() 유지(ledger 갭 9).</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-001_SW 검증 명세서.xlsx
+++ b/Deliverables/Engineering/SoftwareVerification/ENG-SWE6-001_SW 검증 명세서.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -710,7 +710,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) - Phase 3(SWR-003, SWR-018, SWR-020) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
       <c r="G4" s="9" t="str"/>
@@ -1885,6 +1885,635 @@
       <c r="G39" s="49" t="inlineStr">
         <is>
           <t>자동(unittest) — tests_system/test_st_func_swr005_006_007_008_009_017.py::TestSTFUNC0030AllThreeForcedReleaseTriggersSimultaneously.testFireOvertemperatureAdultAllTrueSimultaneouslyStillReleasesBothDoors</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0031</t>
+        </is>
+      </c>
+      <c r="B40" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D40" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, vehicle_speed_kph=2.9(경계값, 3km/h 미만) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E40" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 RELEASE로 유지되어야 한다(자동주행잠금 후보 미생성) - ENG-SWE1-001 4.1절 SWR-003(a) 합격기준의 경계값(2.9km/h) 부정 경로.</t>
+        </is>
+      </c>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis) - 3km/h 임계 미만 경계(2.9km/h)</t>
+        </is>
+      </c>
+      <c r="G40" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0031VehicleSpeedBelowThresholdDoesNotLock.testSpeedJustBelowThresholdKeepsReleasedOutputUnlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0032</t>
+        </is>
+      </c>
+      <c r="B41" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, vehicle_speed_kph=3.0(경계값 자체) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t>전이 첫 평가주기(2주기차)부터 좌/우 확정 출력이 LOCK으로 관측되어야 한다(ENG-SWE1-001 4.1절 SWR-003(a) 합격기준: 경계값 2.9/3.0/3.1km/h 중 3.0km/h 자체 - 이상 조건이 경계값을 포함함을 확인).</t>
+        </is>
+      </c>
+      <c r="F41" s="49" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis) - 3km/h 임계값 자체(3.0km/h)</t>
+        </is>
+      </c>
+      <c r="G41" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0032VehicleSpeedAtThresholdLocksImmediately.testSpeedExactlyAtThresholdLocksFromFirstCycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0033</t>
+        </is>
+      </c>
+      <c r="B42" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, vehicle_speed_kph=3.1(경계값 초과) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr">
+        <is>
+          <t>전이 첫 평가주기부터 좌/우 확정 출력이 LOCK으로 관측되어야 한다(SWR-003(a) 합격기준 경계값 3.1km/h).</t>
+        </is>
+      </c>
+      <c r="F42" s="49" t="inlineStr">
+        <is>
+          <t>경계값분석(Boundary Value Analysis) - 3km/h 임계 초과 경계(3.1km/h)</t>
+        </is>
+      </c>
+      <c r="G42" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0033VehicleSpeedAboveThresholdLocks.testSpeedJustAboveThresholdLocksFromFirstCycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0034</t>
+        </is>
+      </c>
+      <c r="B43" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D43" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: vehicle_speed_kph=10.0, ignition_on=True @ nowS=1.000(LOCK 기준 수립). 2주기차: vehicle_speed_kph=10.0(유지) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E43" s="49" t="inlineStr">
+        <is>
+          <t>두 평가주기 모두 좌/우 확정 출력=LOCK으로 유지되어야 한다(ENG-SWE1-001 4.1절 SWR-003(b) 유지되는 동안 LOCK으로 유지).</t>
+        </is>
+      </c>
+      <c r="F43" s="49" t="inlineStr">
+        <is>
+          <t>상태전이 테스트(State Transition Testing) - LOCK 지속 연속성</t>
+        </is>
+      </c>
+      <c r="G43" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0034VehicleSpeedLockSustainedAcrossCycles.testLockMaintainedWhileSpeedStaysAtOrAboveThreshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0035</t>
+        </is>
+      </c>
+      <c r="B44" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003</t>
+        </is>
+      </c>
+      <c r="C44" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, vehicle_speed_kph=301.0(정의된 유효 범위 0.0~300.0 초과, OUT_OF_RANGE) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>범위 오류 속도 입력이 평가 전에 거절되어 자동주행잠금 후보를 생성하지 않아야 한다(SWR-013(b) 형식/범위 오류 거절 원칙의 SWR-003 입력 재확인). 좌/우 확정 출력=RELEASE 유지.</t>
+        </is>
+      </c>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t>오류추측(Error Guessing) + 동등분할(Equivalence Partitioning) - 범위 오류 무효 클래스</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0035VehicleSpeedOutOfRangeDoesNotLock.testOutOfRangeSpeedValueProducesNoLockCandidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0036</t>
+        </is>
+      </c>
+      <c r="B45" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C45" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, isofix_left=False, isofix_right=False(FF 조합) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 RELEASE로 유지되어야 한다(ENG-SWE1-001 4.1절 SWR-018 검증방안 4가지 조합 중 FF - ISOFIX 강제잠금 로직이 양쪽 모두에 영향 없음).</t>
+        </is>
+      </c>
+      <c r="F45" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) - 좌/우 isofix 2x2(FF/FT/TF/TT) 중 FF</t>
+        </is>
+      </c>
+      <c r="G45" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0036IsofixBothFalseLeavesBothDoorsUnaffected.testBothIsofixFalseKeepsBothDoorsAtPriorReleasedState</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0037</t>
+        </is>
+      </c>
+      <c r="B46" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C46" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D46" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, isofix_left=False, isofix_right=True(FT 조합) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="inlineStr">
+        <is>
+          <t>우측=LOCK, 좌측=RELEASE(변화 없음, 독립 유지)로 관측되어야 한다(SWR-018(a)/(b), 검증방안 FT 조합).</t>
+        </is>
+      </c>
+      <c r="F46" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) - 좌/우 isofix 2x2 중 FT</t>
+        </is>
+      </c>
+      <c r="G46" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0037IsofixLeftFalseRightTrueLocksOnlyRight.testRightIsofixTrueLocksRightOnlyWhileLeftStaysReleased</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0038</t>
+        </is>
+      </c>
+      <c r="B47" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C47" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D47" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, isofix_left=True, isofix_right=False(TF 조합) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E47" s="49" t="inlineStr">
+        <is>
+          <t>좌측=LOCK, 우측=RELEASE(변화 없음, 독립 유지)로 관측되어야 한다(SWR-018(a)/(b), 검증방안 TF 조합, 좌우 대칭 확인).</t>
+        </is>
+      </c>
+      <c r="F47" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) - 좌/우 isofix 2x2 중 TF</t>
+        </is>
+      </c>
+      <c r="G47" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0038IsofixLeftTrueRightFalseLocksOnlyLeft.testLeftIsofixTrueLocksLeftOnlyWhileRightStaysReleased</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0039</t>
+        </is>
+      </c>
+      <c r="B48" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D48" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일, 부팅 직후): isofix_left=True, isofix_right=True(TT 조합), ignition_on=True @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E48" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 LOCK으로 관측되어야 한다(SWR-018(a), 검증방안 TT 조합 - 양쪽 모두 독립적으로 LOCK 전환).</t>
+        </is>
+      </c>
+      <c r="F48" s="49" t="inlineStr">
+        <is>
+          <t>전 조건 조합(Exhaustive Combination) - 좌/우 isofix 2x2 중 TT</t>
+        </is>
+      </c>
+      <c r="G48" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0039IsofixBothTrueLocksBothDoors.testBothIsofixTrueLocksBothDoorsIndependently</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0040</t>
+        </is>
+      </c>
+      <c r="B49" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018</t>
+        </is>
+      </c>
+      <c r="C49" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE 기준 수립). 2주기차: ignition_on=True, isofix_left="TRUE"(불리언이 아닌 형식 오류), isofix_right=True @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>좌측 isofix 형식 오류로 좌측 강제잠금 후보가 생성되지 않아 좌측=RELEASE 유지, 우측은 유효한 TRUE이므로 우측=LOCK으로 관측되어야 한다(SWR-013(b) 형식 오류 거절 원칙 + SWR-018(b) 좌우 독립 결합 확인).</t>
+        </is>
+      </c>
+      <c r="F49" s="49" t="inlineStr">
+        <is>
+          <t>오류추측(Error Guessing) - 형식 오류 무효 클래스(non-bool) + 좌우 독립 결합</t>
+        </is>
+      </c>
+      <c r="G49" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0040IsofixLeftInvalidProducesNoCandidateWhileRightIndependent.testInvalidLeftIsofixFieldDoesNotLockLeftWhileRightStillLocksFromValidTrue</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0041</t>
+        </is>
+      </c>
+      <c r="B50" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020</t>
+        </is>
+      </c>
+      <c r="C50" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D50" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=True @ nowS=1.000(NORMAL 기준 수립). 2주기차: ignition_on=False(TRUE에서 FALSE로 전이) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t>전이 첫 평가주기(2주기차)에 좌/우 확정 출력이 RELEASE로 전환되고, 시스템 상태가 OFF로 전이되며, 정의된 타입의 비공백 ignition_off 이유코드가 제공되어야 한다(ENG-SWE1-001 4.1절 SWR-020(a)). 이유코드는 CycleResult.stateResult.warningReasonCode로 직접 관측 가능(Phase2 이유코드와 달리 구조적 한계 없음).</t>
+        </is>
+      </c>
+      <c r="F50" s="49" t="inlineStr">
+        <is>
+          <t>요구사항 기반 시험(Requirements-based Test) - SWR-020(a) 인수 시나리오</t>
+        </is>
+      </c>
+      <c r="G50" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0041IgnitionOffReleasesAndTransitionsToOffWithReasonCode.testIgnitionOnFalseTransitionReleasesBothDoorsSetsOffStateAndReasonCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0042</t>
+        </is>
+      </c>
+      <c r="B51" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020</t>
+        </is>
+      </c>
+      <c r="C51" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D51" s="49" t="inlineStr">
+        <is>
+          <t>1주기차: ignition_on=False @ nowS=1.000(RELEASE/OFF 기준 수립). 2주기차: ignition_on=False(유지) @ nowS=1.050.</t>
+        </is>
+      </c>
+      <c r="E51" s="49" t="inlineStr">
+        <is>
+          <t>두 평가주기 모두 좌/우 확정 출력=RELEASE, 시스템 상태=OFF로 유지되어야 한다(ENG-SWE1-001 4.1절 SWR-020(b) FALSE로 유지되는 동안 RELEASE로, 시스템 상태를 OFF로 유지).</t>
+        </is>
+      </c>
+      <c r="F51" s="49" t="inlineStr">
+        <is>
+          <t>상태전이 테스트(State Transition Testing) - RELEASE/OFF 지속 연속성</t>
+        </is>
+      </c>
+      <c r="G51" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0042IgnitionOffSustainedAcrossCycles.testReleaseAndOffStateMaintainedWhileIgnitionStaysFalse</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0043</t>
+        </is>
+      </c>
+      <c r="B52" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020 / SWR-013(b)</t>
+        </is>
+      </c>
+      <c r="C52" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D52" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일, 부팅 직후): ignition_on="FALSE"(불리언이 아닌 형식 오류), sensor_fault=False @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>형식 오류 ignition_on은 OFF로 오판정되지 않아야 하며(ENG-SWE3-001 8.8절 SW 설계 재량 확정 - IU-0003/IU-0016 대칭 미판정 재확인), SWR-013(b)에 따라 이 입력이 평가 전 거절되어(IF-0008 게이트) 이번 평가주기의 출력이 어떤 후보도 반영하지 않고 직전 확정값(부팅 기본값 LOCK, LOCK)을 그대로 유지해야 한다.</t>
+        </is>
+      </c>
+      <c r="F52" s="49" t="inlineStr">
+        <is>
+          <t>오류추측(Error Guessing) - 형식 오류 무효 클래스(non-bool ignition_on)</t>
+        </is>
+      </c>
+      <c r="G52" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0043IgnitionOnFieldInvalidDoesNotJudgeOff.testInvalidIgnitionOnFieldDoesNotTransitionToOffAndBlocksArbitration</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0044</t>
+        </is>
+      </c>
+      <c r="B53" s="49" t="inlineStr">
+        <is>
+          <t>SWR-003 / SWR-007</t>
+        </is>
+      </c>
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): crash_status="CONFIRMED"(priority=1, RELEASE), vehicle_speed_kph=20.0(priority=6, LOCK) 동시 주입, ignition_on=True @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 관측되어야 한다(SWR-007(a) 다른 모든 명령보다 우선하여 + ENG-SWE1-001 3장 우선순위 관계 확장 - crash가 자동주행잠금보다 우선. OEM 원문 직접 근거, 추가 OEM-A 확인 불필요).</t>
+        </is>
+      </c>
+      <c r="F53" s="49" t="inlineStr">
+        <is>
+          <t>결정표기반 시험(Command Arbiter 우선순위 결정표, priority 1 vs 6)</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0044CrashConfirmedOutranksAutoDriveLock.testCrashConfirmedReleasesEvenWhileVehicleSpeedRequestsLock</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0045</t>
+        </is>
+      </c>
+      <c r="B54" s="49" t="inlineStr">
+        <is>
+          <t>SWR-018 / SWR-017</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D54" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): fire_detected=True(priority=3, RELEASE), isofix_left=True, isofix_right=True(priority=5, LOCK) 동시 주입, ignition_on=True @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 관측되어야 한다(화재 등 강제해제가 ISOFIX 강제잠금보다 우선). [적용 한계] 이 순서는 탑승자 탈출/구조 보장 취지에 따른 SW 설계 추론이며(ENG-SWE1-001 3장/8장 가정 15), OEM 원문이 직접 규정하지 않아 완전한 OEM 확인은 아니다 - 현재 구현된 우선순위 체인이 설계대로 동작함만 확인한다.</t>
+        </is>
+      </c>
+      <c r="F54" s="49" t="inlineStr">
+        <is>
+          <t>결정표기반 시험(Command Arbiter 우선순위 결정표, priority 3 vs 5)</t>
+        </is>
+      </c>
+      <c r="G54" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0045FireForcedReleaseOutranksIsofixForcedLock.testFireDetectedReleasesEvenWhileIsofixRequestsLock</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0046</t>
+        </is>
+      </c>
+      <c r="B55" s="49" t="inlineStr">
+        <is>
+          <t>SWR-020 / SWR-018 / SWR-003</t>
+        </is>
+      </c>
+      <c r="C55" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D55" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): ignition_on=False(priority=4, RELEASE), isofix_left=True, isofix_right=True(priority=5, LOCK), vehicle_speed_kph=20.0(priority=6, LOCK) 동시 주입 @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E55" s="49" t="inlineStr">
+        <is>
+          <t>좌/우 확정 출력이 모두 RELEASE로 관측되고 시스템 상태=OFF로 전이되어야 한다(ledger 누적 갭 13 대부분 해소 사항 - ignition-off가 ISOFIX/자동주행잠금보다 우선하는 entrapment 방지 취지의 SW 설계 재량, ENG-SWE2-001 9장). state==OFF가 candidateCommands를 제한하지 않고 ignition-off 후보 자체의 우선순위 승리로 RELEASE가 달성된다는 설계 결정의 시스템 수준 재확인.</t>
+        </is>
+      </c>
+      <c r="F55" s="49" t="inlineStr">
+        <is>
+          <t>결정표기반 시험(Command Arbiter 우선순위 결정표, priority 4 vs 5/6, 3중 동시발생)</t>
+        </is>
+      </c>
+      <c r="G55" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0046IgnitionOffOutranksIsofixAndAutoDriveLock.testIgnitionOffReleasesEvenWhileIsofixAndSpeedBothRequestLock</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="49" t="inlineStr">
+        <is>
+          <t>ST-FUNC-0047</t>
+        </is>
+      </c>
+      <c r="B56" s="49" t="inlineStr">
+        <is>
+          <t>SWR-005 / SWR-006 / SWR-020</t>
+        </is>
+      </c>
+      <c r="C56" s="49" t="inlineStr">
+        <is>
+          <t>PC/SIL (ENV-PC-SIL-01)</t>
+        </is>
+      </c>
+      <c r="D56" s="49" t="inlineStr">
+        <is>
+          <t>1주기차(단일): rear_left_approach_risk=True(priority=2, LOCK, ASIL B), ignition_on=False(priority=4, RELEASE, QM) 동시 주입 @ nowS=1.000.</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr">
+        <is>
+          <t>좌측=LOCK(접근위험 승리), 우측=RELEASE(ignition-off 승리, 경쟁 없음), 시스템 상태=OFF로 관측되어야 한다. [단정 금지] 이 우선순위(ASIL B 접근위험이 QM ignition-off보다 이긴다)는 Command Arbiter의 잠정 기본값일 뿐이며(ENG-SWE2-001 9장), OEM-A의 명시적 확인 없이 최종 확정되었다고 단정하지 않는다(ENG-SWE1-001 8장 가정 18, ledger 누적 갭 16). 이 케이스는 현재 동작 재확인 목적이며 요구사항 수용기준으로 주장하지 않는다 - ENG-SWE5-002의 IT-0112/IT-0135와 동일 성격의 시스템 수준 재확인.</t>
+        </is>
+      </c>
+      <c r="F56" s="49" t="inlineStr">
+        <is>
+          <t>결정표기반 시험(Command Arbiter 우선순위 결정표, priority 2 vs 4) - 현재 동작 재확인 전용</t>
+        </is>
+      </c>
+      <c r="G56" s="49" t="inlineStr">
+        <is>
+          <t>자동(unittest) - tests_system/test_st_func_swr003_018_020.py::TestSTFUNC0047ApproachRiskCurrentlyOutranksIgnitionOffOnAffectedDoor.testLeftApproachRiskKeepsLockOnLeftWhileIgnitionOffReleasesRightAndSetsOffState</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2623,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) - Phase 3(SWR-003, SWR-018, SWR-020) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2701,12 @@
       </c>
       <c r="D10" s="49" t="inlineStr">
         <is>
-          <t>SWR-013, SWR-021 블랙박스 시스템 테스트(ST-FUNC-0001~0013) 전량; SWR-005, SWR-006, SWR-007, SWR-008, SWR-009, SWR-017 블랙박스 시스템 테스트(ST-FUNC-0014~0030) 전량(Phase 2, 2026-09-19 추가)</t>
+          <t>SWR-013, SWR-021 블랙박스 시스템 테스트(ST-FUNC-0001~0013) 전량; SWR-005, SWR-006, SWR-007, SWR-008, SWR-009, SWR-017 블랙박스 시스템 테스트(ST-FUNC-0014~0030) 전량(Phase 2, 2026-09-19 추가); SWR-003, SWR-018, SWR-020 블랙박스 시스템 테스트(ST-FUNC-0031~0047) 전량(Phase 3, 2026-09-20 추가)</t>
         </is>
       </c>
       <c r="E10" s="49" t="inlineStr">
         <is>
-          <t>tests_system/test_st_func_swr013_swr021.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-18.txt, 13/13 Pass); tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt, 17/17 unittest 통과 — 단, ST-FUNC-0016은 QA 판정상 요구사항 원문 기준 Fail로 기록됨, ENG-SWE6-002 참조)</t>
+          <t>tests_system/test_st_func_swr013_swr021.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-18.txt, 13/13 Pass); tests_system/test_st_func_swr005_006_007_008_009_017.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-19.txt, 17/17 unittest 통과 — 단, ST-FUNC-0016은 QA 판정상 요구사항 원문 기준 Fail로 기록됨, ENG-SWE6-002 참조); tests_system/test_st_func_swr003_018_020.py (unittest -v 실행 로그: Deliverables/Engineering/SoftwareVerification/evidence/ST-FUNC-run-log_2026-09-20.txt, 17/17 Pass; 전체 회귀 로그: Deliverables/Engineering/SoftwareVerification/evidence/full-regression-run-log_2026-09-20.txt, 324/324 Pass)</t>
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
@@ -2113,7 +2742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2192,7 +2821,7 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>v0.2 (Draft) — Phase 2(SWR-005~009, SWR-017) 갱신, Phase 1 내용 유지</t>
+          <t>v0.3 (Draft) - Phase 3(SWR-003, SWR-018, SWR-020) 갱신, Phase 1/2 내용 유지</t>
         </is>
       </c>
     </row>
@@ -2311,6 +2940,38 @@
         </is>
       </c>
       <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sw-system-tester</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phase 3 시스템 테스트(SWE.6) 명세 갱신 - ST-FUNC-0031~0047 신규 17건(SWR-003 5건[2.9/3.0/3.1km/h 경계값 포함] + SWR-018 5건[좌우 isofix 전 조건 조합 4 + 오류추측 1] + SWR-020 3건[이벤트/상태기반 + ignitionOnField invalid 회귀] + 우선순위 결정표 4건[crash&gt;자동주행잠금, fire&gt;ISOFIX, ignition-off&gt;ISOFIX/자동주행잠금, 접근위험(ASIL B) vs ignition-off(QM) 현재 동작 재확인], ENG-SWE1-001 v0.3 4.1절 기반 블랙박스 케이스). 진입점 InputValidationAdapter.handleCycle() 유지(ledger 갭 9). Phase 3 전체 게이트(SWE.1~SWE.6) 완료.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>초안(검토 미실시)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>
